--- a/data/sars/pacific/tables/Pacific_2022_Appendix2.xlsx
+++ b/data/sars/pacific/tables/Pacific_2022_Appendix2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/pacific/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F0AAF0-55D4-A34D-A52F-00AE8C8103A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4363F5B9-2895-834D-9892-0FF43895EFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3840" yWindow="500" windowWidth="28040" windowHeight="17440" xr2:uid="{0BA51BEC-9DBC-0E4D-B301-5D51AE1356B8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="136">
   <si>
     <t>n/a</t>
   </si>
@@ -176,9 +176,6 @@
     <t>survey3</t>
   </si>
   <si>
-    <t>revised</t>
-  </si>
-  <si>
     <t>species_stock</t>
   </si>
   <si>
@@ -438,13 +435,22 @@
   </si>
   <si>
     <t>Common bottlenose dolphin (O'ahu)</t>
+  </si>
+  <si>
+    <t>revision_yr</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -471,6 +477,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -499,7 +511,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -508,6 +520,7 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -842,7 +855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DA899BF-E69B-5648-9631-8A8F9B7CD1F3}">
-  <dimension ref="A1:N87"/>
+  <dimension ref="A1:O87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="72" style="3" bestFit="1" customWidth="1"/>
@@ -856,13 +869,13 @@
     <col min="9" max="9" width="10.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.83203125" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="7" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="10.83203125" style="3"/>
+    <col min="14" max="15" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>34</v>
@@ -900,13 +913,16 @@
       <c r="M1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="N1" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="N1" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1">
         <v>257606</v>
@@ -948,9 +964,9 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" s="1">
         <v>30968</v>
@@ -992,9 +1008,9 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -1032,9 +1048,9 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>4</v>
@@ -1072,9 +1088,9 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>4</v>
@@ -1112,9 +1128,9 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>4</v>
@@ -1152,9 +1168,9 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B8" s="1">
         <v>187386</v>
@@ -1196,9 +1212,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B9" s="1">
         <v>34187</v>
@@ -1240,9 +1256,9 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B10" s="1">
         <v>14050</v>
@@ -1284,9 +1300,9 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B11" s="5">
         <v>1465</v>
@@ -1327,10 +1343,13 @@
       <c r="N11" s="6">
         <v>2022</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="O11" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B12" s="1">
         <v>4191</v>
@@ -1372,9 +1391,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13" s="1">
         <v>3760</v>
@@ -1416,9 +1435,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B14" s="1">
         <v>7777</v>
@@ -1460,9 +1479,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B15" s="1">
         <v>24685</v>
@@ -1504,9 +1523,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B16" s="1">
         <v>21487</v>
@@ -1548,9 +1567,9 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B17" s="1">
         <v>11233</v>
@@ -1592,9 +1611,9 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B18" s="1">
         <v>16498</v>
@@ -1636,9 +1655,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B19" s="1">
         <v>34999</v>
@@ -1680,9 +1699,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B20" s="1">
         <v>6336</v>
@@ -1724,9 +1743,9 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B21" s="2">
         <v>453</v>
@@ -1768,9 +1787,9 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B22" s="1">
         <v>3477</v>
@@ -1812,9 +1831,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B23" s="1">
         <v>29988</v>
@@ -1856,9 +1875,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B24" s="1">
         <v>1056308</v>
@@ -1900,9 +1919,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B25" s="1">
         <v>83379</v>
@@ -1944,9 +1963,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B26" s="1">
         <v>29285</v>
@@ -1988,9 +2007,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B27" s="2">
         <v>300</v>
@@ -2032,9 +2051,9 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B28" s="6">
         <v>74</v>
@@ -2075,10 +2094,13 @@
       <c r="N28" s="6">
         <v>2022</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="O28" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B29" s="2">
         <v>836</v>
@@ -2120,9 +2142,9 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B30" s="1">
         <v>1363</v>
@@ -2164,9 +2186,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B31" s="1">
         <v>3044</v>
@@ -2208,9 +2230,9 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B32" s="5">
         <v>5454</v>
@@ -2251,10 +2273,13 @@
       <c r="N32" s="6">
         <v>2022</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B33" s="1">
         <v>4111</v>
@@ -2296,9 +2321,9 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>4</v>
@@ -2340,9 +2365,9 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B35" s="1">
         <v>1997</v>
@@ -2384,9 +2409,9 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B36" s="1">
         <v>26960</v>
@@ -2428,9 +2453,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B37" s="2">
         <v>290</v>
@@ -2472,9 +2497,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B38" s="5">
         <v>1496</v>
@@ -2515,10 +2540,13 @@
       <c r="N38" s="6">
         <v>2022</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="O38" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B39" s="5">
         <v>3477</v>
@@ -2559,10 +2587,13 @@
       <c r="N39" s="6">
         <v>2022</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="O39" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B40" s="1">
         <v>1898</v>
@@ -2604,9 +2635,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B41" s="1">
         <v>11065</v>
@@ -2648,9 +2679,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B42" s="2">
         <v>519</v>
@@ -2692,9 +2723,9 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B43" s="2">
         <v>915</v>
@@ -2736,9 +2767,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>4</v>
@@ -2780,9 +2811,9 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B45" s="1">
         <v>76375</v>
@@ -2824,9 +2855,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>4</v>
@@ -2868,9 +2899,9 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B47" s="1">
         <v>7385</v>
@@ -2912,9 +2943,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>4</v>
@@ -2958,7 +2989,7 @@
     </row>
     <row r="49" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>4</v>
@@ -3002,7 +3033,7 @@
     </row>
     <row r="50" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>4</v>
@@ -3046,7 +3077,7 @@
     </row>
     <row r="51" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>4</v>
@@ -3090,7 +3121,7 @@
     </row>
     <row r="52" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>4</v>
@@ -3134,7 +3165,7 @@
     </row>
     <row r="53" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B53" s="1">
         <v>39798</v>
@@ -3178,7 +3209,7 @@
     </row>
     <row r="54" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>4</v>
@@ -3218,7 +3249,7 @@
     </row>
     <row r="55" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>4</v>
@@ -3258,7 +3289,7 @@
     </row>
     <row r="56" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>4</v>
@@ -3298,7 +3329,7 @@
     </row>
     <row r="57" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B57" s="2">
         <v>665</v>
@@ -3342,7 +3373,7 @@
     </row>
     <row r="58" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>0</v>
@@ -3386,7 +3417,7 @@
     </row>
     <row r="59" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>0</v>
@@ -3430,7 +3461,7 @@
     </row>
     <row r="60" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>4</v>
@@ -3472,7 +3503,7 @@
     </row>
     <row r="61" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>4</v>
@@ -3514,7 +3545,7 @@
     </row>
     <row r="62" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>4</v>
@@ -3554,7 +3585,7 @@
     </row>
     <row r="63" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>4</v>
@@ -3594,7 +3625,7 @@
     </row>
     <row r="64" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B64" s="1">
         <v>35179</v>
@@ -3638,7 +3669,7 @@
     </row>
     <row r="65" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B65" s="1">
         <v>40960</v>
@@ -3682,7 +3713,7 @@
     </row>
     <row r="66" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B66" s="1">
         <v>40647</v>
@@ -3726,7 +3757,7 @@
     </row>
     <row r="67" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>4</v>
@@ -3770,7 +3801,7 @@
     </row>
     <row r="68" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B68" s="1">
         <v>10328</v>
@@ -3814,7 +3845,7 @@
     </row>
     <row r="69" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B69" s="2">
         <v>477</v>
@@ -3858,7 +3889,7 @@
     </row>
     <row r="70" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B70" s="1">
         <v>2086</v>
@@ -3902,7 +3933,7 @@
     </row>
     <row r="71" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B71" s="2">
         <v>167</v>
@@ -3946,7 +3977,7 @@
     </row>
     <row r="72" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B72" s="1">
         <v>1329</v>
@@ -3986,7 +4017,7 @@
     </row>
     <row r="73" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>4</v>
@@ -4030,7 +4061,7 @@
     </row>
     <row r="74" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B74" s="2">
         <v>161</v>
@@ -4074,7 +4105,7 @@
     </row>
     <row r="75" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B75" s="1">
         <v>12607</v>
@@ -4118,7 +4149,7 @@
     </row>
     <row r="76" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B76" s="1">
         <v>1132</v>
@@ -4162,7 +4193,7 @@
     </row>
     <row r="77" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B77" s="1">
         <v>2550</v>
@@ -4206,7 +4237,7 @@
     </row>
     <row r="78" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B78" s="1">
         <v>4431</v>
@@ -4250,7 +4281,7 @@
     </row>
     <row r="79" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B79" s="1">
         <v>42083</v>
@@ -4294,7 +4325,7 @@
     </row>
     <row r="80" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>4</v>
@@ -4338,7 +4369,7 @@
     </row>
     <row r="81" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B81" s="1">
         <v>5707</v>
@@ -4382,7 +4413,7 @@
     </row>
     <row r="82" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B82" s="2">
         <v>133</v>
@@ -4424,7 +4455,7 @@
     </row>
     <row r="83" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B83" s="2">
         <v>203</v>
@@ -4468,7 +4499,7 @@
     </row>
     <row r="84" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B84" s="2">
         <v>602</v>
@@ -4512,7 +4543,7 @@
     </row>
     <row r="85" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B85" s="2">
         <v>391</v>
@@ -4556,7 +4587,7 @@
     </row>
     <row r="86" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B86" s="2">
         <v>438</v>
@@ -4600,7 +4631,7 @@
     </row>
     <row r="87" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>4</v>
